--- a/public/ListeParticipantsTournoiInterfiliales2026.xlsx
+++ b/public/ListeParticipantsTournoiInterfiliales2026.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenove\OneDrive\Bureau\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenove\participants-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C65DD473-E5B7-445A-B7E2-E193B2D3E74F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB71921-9F61-4E10-88FB-F2A29235D8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1624" uniqueCount="462">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1634" uniqueCount="464">
   <si>
     <t>Disciplines</t>
   </si>
@@ -1411,13 +1411,19 @@
   </si>
   <si>
     <t>hanae.moumene@veolia.com</t>
+  </si>
+  <si>
+    <t>Mohamed FENNICH</t>
+  </si>
+  <si>
+    <t>mohamed.fennich@veolia.com</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -1451,8 +1457,14 @@
       <color rgb="FF000000"/>
       <name val="Arial"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1463,6 +1475,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF38761D"/>
         <bgColor rgb="FF38761D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
   </fills>
@@ -1493,7 +1511,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1530,6 +1548,15 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="6" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -10447,17 +10474,39 @@
       <c r="Y177" s="2"/>
     </row>
     <row r="178" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="2"/>
-      <c r="B178" s="2"/>
-      <c r="C178" s="2"/>
-      <c r="D178" s="2"/>
-      <c r="E178" s="12"/>
-      <c r="F178" s="2"/>
-      <c r="G178" s="2"/>
-      <c r="H178" s="2"/>
-      <c r="I178" s="2"/>
-      <c r="J178" s="2"/>
-      <c r="K178" s="2"/>
+      <c r="A178" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B178" s="3" t="s">
+        <v>462</v>
+      </c>
+      <c r="C178" s="15" t="s">
+        <v>42</v>
+      </c>
+      <c r="D178" s="3" t="s">
+        <v>463</v>
+      </c>
+      <c r="E178" s="4" t="s">
+        <v>336</v>
+      </c>
+      <c r="F178" s="9" t="s">
+        <v>28</v>
+      </c>
+      <c r="G178" s="13">
+        <v>46156</v>
+      </c>
+      <c r="H178" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="I178" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="J178" s="14" t="s">
+        <v>19</v>
+      </c>
+      <c r="K178" s="6" t="s">
+        <v>19</v>
+      </c>
       <c r="L178" s="2"/>
       <c r="M178" s="2"/>
       <c r="N178" s="2"/>

--- a/public/ListeParticipantsTournoiInterfiliales2026.xlsx
+++ b/public/ListeParticipantsTournoiInterfiliales2026.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lenove\participants-app\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BB71921-9F61-4E10-88FB-F2A29235D8DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6D00429-DF13-4EC4-8BCF-DA23599F7F01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
